--- a/data/trans_orig/P21D_4_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P21D_4_R-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria psicológica, no la pudo recibir por motivos económicos en 2023</t>
+          <t>Población que, necesitando atención sanitaria psicológica, no la pudo recibir por motivos económicos en 2023 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,97 +730,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4544</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2861</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3690</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>199405</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>137485</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>140346</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>340604</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>344294</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1073,97 +1073,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2498</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2689</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>10837</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>3,72%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>2498</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>9347</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>9367</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>3,21%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>2498</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>8313</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>281772</t>
+          <t>280282</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>487528</t>
+          <t>486474</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>639</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>6021</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>700</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6167</t>
+          <t>5822</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>213632</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>251141</t>
+          <t>251668</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>256978</t>
+          <t>257050</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>467008</t>
+          <t>467353</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>472491</t>
+          <t>472475</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,85%</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6206</t>
+          <t>6401</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>608</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>5385</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>640</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8347</t>
+          <t>8757</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>520352</t>
+          <t>520157</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>315384</t>
+          <t>315477</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>320862</t>
+          <t>320254</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>839072</t>
+          <t>838662</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>846923</t>
+          <t>846779</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>99,92%</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6058</t>
+          <t>5943</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7417</t>
+          <t>7712</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2346</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10447</t>
+          <t>10350</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>232446</t>
+          <t>232561</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>219275</t>
+          <t>218980</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>225377</t>
+          <t>225355</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>454749</t>
+          <t>454846</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>462850</t>
+          <t>462787</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>934</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5859</t>
+          <t>5629</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6127</t>
+          <t>5777</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>155119</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>156354</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>179418</t>
+          <t>179648</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>184353</t>
+          <t>184343</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>335504</t>
+          <t>335854</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>340580</t>
+          <t>340526</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,68%</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3120</t>
+          <t>2810</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,62 +2823,62 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>946</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>3595</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>3218</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>115086</t>
+          <t>115396</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>169103</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>170049</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>285038</t>
+          <t>284661</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>796</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8695</t>
+          <t>9442</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8255</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20783</t>
+          <t>21203</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>10170</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>24816</t>
+          <t>26447</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1655083</t>
+          <t>1654336</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1663102</t>
+          <t>1662982</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,96%</t>
+          <t>99,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1571251</t>
+          <t>1570831</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1583779</t>
+          <t>1584206</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3230996</t>
+          <t>3229365</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3245895</t>
+          <t>3245642</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D_4_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P21D_4_R-Edad-trans_orig.xlsx
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>210781</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>140346</t>
+          <t>162985</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>344294</t>
+          <t>373766</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>210781</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>210781</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>210781</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>140346</t>
+          <t>162985</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>140346</t>
+          <t>162985</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140346</t>
+          <t>162985</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>344294</t>
+          <t>373766</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>344294</t>
+          <t>373766</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>344294</t>
+          <t>373766</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2498</t>
+          <t>2503</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1113,12 +1113,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10837</t>
+          <t>9878</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2498</t>
+          <t>2503</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1148,12 +1148,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9367</t>
+          <t>9365</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>226813</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1216,27 +1216,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>288621</t>
+          <t>247851</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>280282</t>
+          <t>240476</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>291119</t>
+          <t>250354</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1251,27 +1251,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>493343</t>
+          <t>474663</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>486474</t>
+          <t>467801</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>495841</t>
+          <t>477166</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>226813</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>226813</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>226813</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>291119</t>
+          <t>250354</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>291119</t>
+          <t>250354</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>291119</t>
+          <t>250354</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>495841</t>
+          <t>477166</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>495841</t>
+          <t>477166</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>495841</t>
+          <t>477166</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2530</t>
+          <t>2664</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>798</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6021</t>
+          <t>6325</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,22 +1481,22 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2530</t>
+          <t>2664</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>819</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5822</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>252518</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>255159</t>
+          <t>293971</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>251668</t>
+          <t>290310</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>257050</t>
+          <t>295837</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,27 +1594,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>470645</t>
+          <t>546489</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>467353</t>
+          <t>542607</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>472475</t>
+          <t>548334</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>252518</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>252518</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>252518</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>257689</t>
+          <t>296635</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>257689</t>
+          <t>296635</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>257689</t>
+          <t>296635</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>473175</t>
+          <t>549153</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>473175</t>
+          <t>549153</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>473175</t>
+          <t>549153</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6401</t>
+          <t>5671</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1779,77 +1779,77 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2044</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5484</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>3188</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>8056</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>1,22%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>608</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5385</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>3142</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>640</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>8757</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -1867,102 +1867,102 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>525444</t>
+          <t>315923</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>520157</t>
+          <t>311397</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>526558</t>
+          <t>317068</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>98,21%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>343764</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>340324</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>345136</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>99,41%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,41%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>99,81%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>820</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>659687</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>654819</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>662180</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>99,52%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>98,78%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>318834</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>315477</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>320254</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,37%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,32%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,81%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>820</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>844277</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>838662</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>846779</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>98,97%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,9%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>526558</t>
+          <t>317068</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>526558</t>
+          <t>317068</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>526558</t>
+          <t>317068</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>320862</t>
+          <t>345808</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>320862</t>
+          <t>345808</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>320862</t>
+          <t>345808</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>847419</t>
+          <t>662875</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>847419</t>
+          <t>662875</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>847419</t>
+          <t>662875</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>1654</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5943</t>
+          <t>6859</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3390</t>
+          <t>3841</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>7886</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5087</t>
+          <t>5495</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>2362</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10350</t>
+          <t>10572</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -2210,27 +2210,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>236807</t>
+          <t>255827</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>232561</t>
+          <t>250622</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>238504</t>
+          <t>257481</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>223302</t>
+          <t>249612</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>218980</t>
+          <t>245567</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>225355</t>
+          <t>252106</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>460109</t>
+          <t>505439</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>454846</t>
+          <t>500362</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>462787</t>
+          <t>508572</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>238504</t>
+          <t>257481</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>238504</t>
+          <t>257481</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>238504</t>
+          <t>257481</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>226692</t>
+          <t>253453</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>226692</t>
+          <t>253453</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>226692</t>
+          <t>253453</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>465196</t>
+          <t>510934</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>465196</t>
+          <t>510934</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>465196</t>
+          <t>510934</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2620</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5629</t>
+          <t>7093</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,22 +2510,22 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2620</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5777</t>
+          <t>6584</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>156354</t>
+          <t>174053</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>182657</t>
+          <t>195750</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>179648</t>
+          <t>191888</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>184343</t>
+          <t>197613</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,27 +2623,27 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>339011</t>
+          <t>369804</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>335854</t>
+          <t>366451</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>340526</t>
+          <t>371851</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>156354</t>
+          <t>174053</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>156354</t>
+          <t>174053</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>156354</t>
+          <t>174053</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>185277</t>
+          <t>198981</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>185277</t>
+          <t>198981</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>185277</t>
+          <t>198981</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>341631</t>
+          <t>373035</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>341631</t>
+          <t>373035</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>341631</t>
+          <t>373035</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>586</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2810</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>586</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3595</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -2896,27 +2896,27 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>117636</t>
+          <t>128975</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>115396</t>
+          <t>126379</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>118206</t>
+          <t>129561</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>170049</t>
+          <t>186159</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2966,27 +2966,27 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>287686</t>
+          <t>315134</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>284661</t>
+          <t>312782</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>288256</t>
+          <t>315720</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>118206</t>
+          <t>129561</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>118206</t>
+          <t>129561</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>118206</t>
+          <t>129561</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>170049</t>
+          <t>186159</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>170049</t>
+          <t>186159</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>170049</t>
+          <t>186159</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>288256</t>
+          <t>315720</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>288256</t>
+          <t>315720</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>288256</t>
+          <t>315720</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>1149</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9442</t>
+          <t>8584</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,67 +3161,67 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>13066</t>
+          <t>14282</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7828</t>
+          <t>8822</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21203</t>
+          <t>21994</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>17667</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>11739</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>26607</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
           <t>0,82%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>16447</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>10170</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>26447</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1660397</t>
+          <t>1564889</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1654336</t>
+          <t>1559690</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1662982</t>
+          <t>1567125</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>99,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,67 +3274,67 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1578968</t>
+          <t>1680092</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1570831</t>
+          <t>1672380</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1584206</t>
+          <t>1685552</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
+          <t>99,16%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>98,7%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>99,48%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>3807</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>3244981</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>3236041</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>3250909</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>99,46%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>99,18%</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>98,67%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>99,51%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>3807</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>3239365</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>3229365</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>3245642</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>99,49%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>99,19%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1592034</t>
+          <t>1694374</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1592034</t>
+          <t>1694374</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1592034</t>
+          <t>1694374</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>3255812</t>
+          <t>3262648</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3255812</t>
+          <t>3262648</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3255812</t>
+          <t>3262648</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
